--- a/medical_surveys_questionnaires/038_patient_participation_in_decision_making_survey--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/038_patient_participation_in_decision_making_survey--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -538,69 +538,69 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>decision_participatoin_instructions</t>
+          <t>medical_condition</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Decision Participatoin Instructions</t>
+          <t>What is your medical condition?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>medical_condition</t>
+          <t>treatment_plan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Medical Condition</t>
+          <t>What is your treatment plan?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>treatment_plan</t>
+          <t>medication_use</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Treatment Plan</t>
+          <t>What medication are you currently using?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>medication_use</t>
+          <t>patient_preference</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Medication Use</t>
+          <t>What is your preference regarding medical decisions?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>patient_preference</t>
+          <t>family_support</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Patient Preference</t>
+          <t>How involved is your family in medical decisions?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>family_support</t>
+          <t>healthcare_coverage</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Family Support</t>
+          <t>What type of healthcare coverage do you have?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>healthcare_coverage</t>
+          <t>patient_communication</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Healthcare Coverage</t>
+          <t>What is your preferred language of communication?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>patient_communication</t>
+          <t>patient_communication_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Patient Communication</t>
+          <t>How would you like to receive communication about your medical treatment?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>patient_communication_2</t>
+          <t>patient_preference_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patient Communication 2</t>
+          <t>Patient Preference 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>patient_communication_3</t>
+          <t>family_support_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Patient Communication 3</t>
+          <t>Family Support 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,317 +773,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>patient_preference_2</t>
+          <t>healthcare_coverage_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Patient Preference 2</t>
+          <t>Healthcare Coverage 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>family_support_2</t>
+          <t>submit_form</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Family Support 2</t>
+          <t>Submit Form</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>healthcare_coverage_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Healthcare Coverage 2</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>patient_communication_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Patient Communication 2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>patient_preference_3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Patient Preference 3</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>family_support_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Family Support 2</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>healthcare_coverage_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Healthcare Coverage 2</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>patient_communication_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Patient Communication 3</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>patient_preference_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Patient Preference 4</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>family_support_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Family Support 3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>healthcare_coverage_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Healthcare Coverage 3</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>patient_communication_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Patient Communication 4</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>patient_preference_5</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Patient Preference 5</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit_form</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submit Form</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +822,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'acute_coronary_syndrome'}</t>
+          <t>acute_coronary_syndrome</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Acute Coronary Syndrome'}</t>
+          <t>Acute Coronary Syndrome</t>
         </is>
       </c>
     </row>
@@ -1148,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'acute_ischemic_stroke'}</t>
+          <t>acute_ischemic_stroke</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Acute Ischemic Stroke'}</t>
+          <t>Acute Ischemic Stroke</t>
         </is>
       </c>
     </row>
@@ -1165,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'acute_myocardial_infarction'}</t>
+          <t>acute_myocardial_infarction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Acute Myocardial Infarction'}</t>
+          <t>Acute Myocardial Infarction</t>
         </is>
       </c>
     </row>
@@ -1182,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1199,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'cardiac_rehabilitation_program'}</t>
+          <t>cardiac_rehabilitation_program</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Cardiac Rehabilitation Program'}</t>
+          <t>Cardiac Rehabilitation Program</t>
         </is>
       </c>
     </row>
@@ -1216,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'coronary_angioplasty/stenting'}</t>
+          <t>coronary_angioplasty/stenting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Coronary Angioplasty/Stenting'}</t>
+          <t>Coronary Angioplasty/Stenting</t>
         </is>
       </c>
     </row>
@@ -1233,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'coronary_artery_bypass_graft'}</t>
+          <t>coronary_artery_bypass_graft</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Coronary Artery Bypass Graft'}</t>
+          <t>Coronary Artery Bypass Graft</t>
         </is>
       </c>
     </row>
@@ -1250,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1267,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'aspirin'}</t>
+          <t>aspirin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Aspirin'}</t>
+          <t>Aspirin</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'do_not_want_to_know'}</t>
+          <t>do_not_want_to_know</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Do Not Want To Know'}</t>
+          <t>Do Not Want To Know</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'would_like_to_know'}</t>
+          <t>would_like_to_know</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Would Like To Know'}</t>
+          <t>Would Like To Know</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'family_involved'}</t>
+          <t>family_involved</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Family Involved'}</t>
+          <t>Family Involved</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'not_involved'}</t>
+          <t>not_involved</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Not Involved'}</t>
+          <t>Not Involved</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'public'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Public'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1420,29 +1144,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>patient_communication_2_choices</t>
+          <t>patient_communication_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'english'}</t>
+          <t>other_language</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'English'}</t>
+          <t>Other Language</t>
         </is>
       </c>
     </row>
@@ -1454,63 +1178,63 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'other_language'}</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Other Language'}</t>
+          <t>Text Message</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>patient_communication_3_choices</t>
+          <t>patient_communication_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'english'}</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'English'}</t>
+          <t>Phone Call</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>patient_communication_3_choices</t>
+          <t>patient_communication_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'other_language'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Other Language'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>patient_preference_2_choices</t>
+          <t>patient_communication_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'would_like_to_know'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Would Like To Know'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1246,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'do_not_want_to_know'}</t>
+          <t>do_not_want_to_know</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Do Not Want To Know'}</t>
+          <t>Do Not Want To Know</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>family_support_2_choices</t>
+          <t>patient_preference_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'family_involved'}</t>
+          <t>would_like_to_know</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Family Involved'}</t>
+          <t>Would Like To Know</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1280,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'not_involved'}</t>
+          <t>family_involved</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Not Involved'}</t>
+          <t>Family Involved</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>healthcare_coverage_2_choices</t>
+          <t>family_support_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'private'}</t>
+          <t>not_involved</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Private'}</t>
+          <t>Not Involved</t>
         </is>
       </c>
     </row>
@@ -1590,352 +1314,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'public'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Public'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>patient_communication_2_choices</t>
+          <t>healthcare_coverage_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'english'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'English'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>patient_communication_2_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'label':_'other_language'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'label': 'Other Language'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>patient_preference_3_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'label':_'do_not_want_to_know'}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'label': 'Do Not Want To Know'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>patient_preference_3_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'label':_'would_like_to_know'}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'label': 'Would Like To Know'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>family_support_2_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'label':_'family_involved'}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'label': 'Family Involved'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>family_support_2_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'label':_'not_involved'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'label': 'Not Involved'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>healthcare_coverage_2_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'label':_'private'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'label': 'Private'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>healthcare_coverage_2_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'label':_'public'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'label': 'Public'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>patient_communication_3_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'label':_'english'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'label': 'English'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>patient_communication_3_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'label':_'other_language'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'label': 'Other Language'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>patient_preference_4_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'label':_'do_not_want_to_know'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'label': 'Do Not Want To Know'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>patient_preference_4_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'label':_'would_like_to_know'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'label': 'Would Like To Know'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>family_support_3_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'label':_'family_involved'}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'label': 'Family Involved'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>family_support_3_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'label':_'not_involved'}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'label': 'Not Involved'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>healthcare_coverage_3_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{'label':_'private'}</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>{'label': 'Private'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>healthcare_coverage_3_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>{'label':_'public'}</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>{'label': 'Public'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>patient_communication_4_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{'label':_'english'}</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>{'label': 'English'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>patient_communication_4_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>{'label':_'other_language'}</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>{'label': 'Other Language'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>patient_preference_5_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>{'label':_'do_not_want_to_know'}</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>{'label': 'Do Not Want To Know'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>patient_preference_5_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>{'label':_'would_like_to_know'}</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>{'label': 'Would Like To Know'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
